--- a/backend/data/financials_by_company/017480.KQ.xlsx
+++ b/backend/data/financials_by_company/017480.KQ.xlsx
@@ -3570,162 +3570,162 @@
       </c>
       <c r="CX1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
         <is>
           <t>shortName</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="ED1" t="inlineStr">
@@ -3822,34 +3822,34 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>4695</v>
+        <v>4810</v>
       </c>
       <c r="T2" t="n">
-        <v>4695</v>
+        <v>4810</v>
       </c>
       <c r="U2" t="n">
-        <v>4645</v>
+        <v>4705</v>
       </c>
       <c r="V2" t="n">
-        <v>4700</v>
+        <v>4865</v>
       </c>
       <c r="W2" t="n">
-        <v>4695</v>
+        <v>4810</v>
       </c>
       <c r="X2" t="n">
-        <v>4695</v>
+        <v>4810</v>
       </c>
       <c r="Y2" t="n">
-        <v>4645</v>
+        <v>4705</v>
       </c>
       <c r="Z2" t="n">
-        <v>4700</v>
+        <v>4865</v>
       </c>
       <c r="AA2" t="n">
         <v>300</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.39</v>
+        <v>6.24</v>
       </c>
       <c r="AC2" t="n">
         <v>1766966400</v>
@@ -3858,31 +3858,31 @@
         <v>0.71769994</v>
       </c>
       <c r="AE2" t="n">
-        <v>5.67</v>
+        <v>5.72</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.308</v>
+        <v>0.316</v>
       </c>
       <c r="AG2" t="n">
-        <v>4226</v>
+        <v>56446</v>
       </c>
       <c r="AH2" t="n">
-        <v>4226</v>
+        <v>56446</v>
       </c>
       <c r="AI2" t="n">
-        <v>115182</v>
+        <v>124940</v>
       </c>
       <c r="AJ2" t="n">
-        <v>92606</v>
+        <v>72614</v>
       </c>
       <c r="AK2" t="n">
-        <v>92606</v>
+        <v>72614</v>
       </c>
       <c r="AL2" t="n">
-        <v>4640</v>
+        <v>4755</v>
       </c>
       <c r="AM2" t="n">
-        <v>4645</v>
+        <v>4795</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>71732224000</v>
+        <v>74048659456</v>
       </c>
       <c r="AQ2" t="n">
-        <v>74203086450</v>
+        <v>75129659850</v>
       </c>
       <c r="AR2" t="n">
         <v>4110</v>
@@ -3909,13 +3909,13 @@
         <v>525</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.32163218</v>
+        <v>0.33201858</v>
       </c>
       <c r="AW2" t="n">
-        <v>4892.7</v>
+        <v>4868</v>
       </c>
       <c r="AX2" t="n">
-        <v>4633.975</v>
+        <v>4631.3</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-39560495104</v>
+        <v>-38016208896</v>
       </c>
       <c r="BB2" t="n">
         <v>0.03352</v>
@@ -3970,16 +3970,16 @@
         <v>1072656000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.177</v>
+        <v>-0.17</v>
       </c>
       <c r="BP2" t="n">
-        <v>-4.948</v>
+        <v>-4.755</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.04570186</v>
+        <v>0.05482459</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BS2" t="n">
         <v>300</v>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>4645</v>
+        <v>4795</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -4092,122 +4092,122 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CX2" t="n">
-        <v>-1.0649627</v>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="CY2" t="n">
-        <v>4645</v>
+        <v>1783060214</v>
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>KOE</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
+          <t>Asia/Seoul</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>KST</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>32400000</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>kr_market</t>
+        </is>
+      </c>
+      <c r="DE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>-0.3118503</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>4795</v>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>979084800000</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-15</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>4705.0 - 4865.0</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>124940</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>685</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.16666667</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>4110.0 - 6140.0</t>
+        </is>
+      </c>
+      <c r="DR2" t="n">
+        <v>-1345</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.21905537</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>5.482459</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-73</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.014995892</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>163.7002</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.03534649</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>20</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>Samhyun Steel Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
           <t>SAMSCO</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>-50</v>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>4645.0 - 4700.0</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>115182</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>535</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>0.13017032</v>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>4110.0 - 6140.0</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>-1495</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.24348535</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>4.570186</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-247.7002</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.050626483</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>11.024902</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0.0023791457</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>20</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="DR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>979084800000</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DV2" t="n">
-        <v>1782174813</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>KOE</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>Asia/Seoul</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>KST</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>32400000</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>kr_market</t>
-        </is>
-      </c>
-      <c r="EB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>Samhyun Steel Co., Ltd.</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr"/>
